--- a/Result/profitability/3257.xlsx
+++ b/Result/profitability/3257.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM69"/>
+  <dimension ref="A1:AM70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.72</v>
       </c>
       <c r="M2" t="n">
-        <v>0.65</v>
+        <v>0.6425000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>48.46625</v>
+        <v>47.73625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.92</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.71375</v>
       </c>
       <c r="N3" t="n">
-        <v>48.9725</v>
+        <v>47.79125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.05</v>
       </c>
       <c r="M4" t="n">
-        <v>0.65</v>
+        <v>0.6275000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>46.97875</v>
+        <v>45.3875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.8</v>
       </c>
       <c r="M5" t="n">
-        <v>0.67</v>
+        <v>0.6162500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>45.93375</v>
+        <v>44.41</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.66</v>
+        <v>0.5775</v>
       </c>
       <c r="N6" t="n">
-        <v>45.47375</v>
+        <v>44.48</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.8</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6200000000000001</v>
+        <v>0.58125</v>
       </c>
       <c r="N7" t="n">
-        <v>44.865</v>
+        <v>44.3325</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.61</v>
+        <v>0.6437499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>44.34125</v>
+        <v>43.825</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9191,6 +9191,133 @@
       </c>
       <c r="AM69" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>3257</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>172</v>
+      </c>
+      <c r="D70" t="n">
+        <v>102</v>
+      </c>
+      <c r="E70" t="n">
+        <v>70</v>
+      </c>
+      <c r="F70" t="n">
+        <v>40.85</v>
+      </c>
+      <c r="G70" t="n">
+        <v>12</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>7.10%</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>30</v>
+      </c>
+      <c r="J70" t="n">
+        <v>42</v>
+      </c>
+      <c r="K70" t="n">
+        <v>36</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.6175</v>
+      </c>
+      <c r="N70" t="n">
+        <v>47.91875</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
+      </c>
+      <c r="V70" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="X70" t="n">
+        <v>1.421052631578947</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>-4.129999999999995</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>-0.09181858603823911</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>-0.4831460674157303</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>-12.19</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>-0.2298265460030166</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK70" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
